--- a/begunici/app_types/animals/excel_templates/Akt_na_perevod_zhivotnykh.xlsx
+++ b/begunici/app_types/animals/excel_templates/Akt_na_perevod_zhivotnykh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2DDD37-A720-43E8-8960-E135DCF79158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE0C1A2-B2CB-4304-A70F-64C08E71C6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Организация</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">в </t>
+  </si>
+  <si>
+    <t>Состояние</t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -553,17 +556,93 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -574,89 +653,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1017,8 +1030,8 @@
       <c r="J4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
     </row>
     <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G5" s="4" t="s">
@@ -1027,11 +1040,11 @@
     </row>
     <row r="6" spans="1:22" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="S6" s="3"/>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
     </row>
     <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -1040,16 +1053,16 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
@@ -1057,11 +1070,11 @@
         <v>13</v>
       </c>
       <c r="S7" s="2"/>
-      <c r="T7" s="54" t="s">
+      <c r="T7" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="U7" s="55"/>
-      <c r="V7" s="56"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="45"/>
     </row>
     <row r="8" spans="1:22" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -1070,16 +1083,16 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
@@ -1097,29 +1110,29 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="S9" s="3"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="53"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="42"/>
     </row>
     <row r="10" spans="1:22" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1129,75 +1142,75 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="53"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="42"/>
     </row>
     <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="53"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="42"/>
     </row>
     <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="53"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="42"/>
     </row>
     <row r="13" spans="1:22" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -1205,25 +1218,25 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="57"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="59"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="49"/>
     </row>
     <row r="14" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -1259,98 +1272,106 @@
       <c r="G15" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
       <c r="M15" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
     <row r="16" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="39" t="s">
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="64"/>
+      <c r="I17" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="40"/>
-      <c r="I17" s="39" t="s">
+      <c r="J17" s="31"/>
+      <c r="K17" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="J17" s="40"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="42"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="34"/>
     </row>
     <row r="19" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="24"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="34"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="62"/>
     </row>
     <row r="20" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
-      <c r="B20" s="31" t="s">
+      <c r="A20" s="55"/>
+      <c r="B20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="60"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="25"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="23"/>
       <c r="N20" s="23"/>
     </row>
     <row r="21" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="29"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
       <c r="N21" s="23"/>
     </row>
     <row r="22" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1383,67 +1404,67 @@
       <c r="A23" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="17"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
       <c r="H23" s="17"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
       <c r="N23" s="7" t="s">
         <v>19</v>
       </c>
       <c r="O23" s="2"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="50"/>
+      <c r="V23" s="50"/>
+      <c r="W23" s="50"/>
+      <c r="X23" s="50"/>
     </row>
     <row r="24" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="27"/>
+      <c r="C24" s="36"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
-      <c r="P24" s="27" t="s">
+      <c r="P24" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="Q24" s="27"/>
+      <c r="Q24" s="36"/>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
-      <c r="T24" s="27" t="s">
+      <c r="T24" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="27"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
     </row>
     <row r="25" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
@@ -1452,62 +1473,62 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
       <c r="N25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50"/>
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
+      <c r="U25" s="50"/>
+      <c r="V25" s="50"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="50"/>
     </row>
     <row r="26" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="27" t="s">
+      <c r="I26" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
-      <c r="Q26" s="27" t="s">
+      <c r="Q26" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="R26" s="27"/>
+      <c r="R26" s="36"/>
       <c r="S26" s="8"/>
       <c r="T26" s="8"/>
-      <c r="U26" s="27" t="s">
+      <c r="U26" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
     </row>
     <row r="27" spans="1:24" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
@@ -1519,11 +1540,11 @@
       <c r="E27" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
       <c r="K27" s="19">
         <v>20</v>
       </c>
@@ -1573,6 +1594,43 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="T23:X23"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="I26:M26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="I24:M24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="I23:M23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D9:P9"/>
+    <mergeCell ref="D13:R13"/>
+    <mergeCell ref="C12:R12"/>
+    <mergeCell ref="B11:R11"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G17:H18"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:F18"/>
     <mergeCell ref="K4:L4"/>
@@ -1588,43 +1646,6 @@
     <mergeCell ref="T12:V12"/>
     <mergeCell ref="T11:V11"/>
     <mergeCell ref="G7:N7"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D9:P9"/>
-    <mergeCell ref="D13:R13"/>
-    <mergeCell ref="C12:R12"/>
-    <mergeCell ref="B11:R11"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="I24:M24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="I23:M23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="F27:J27"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="T23:X23"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="I25:M25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="I26:M26"/>
-    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.59055118110236227" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="85" orientation="landscape" r:id="rId1"/>
